--- a/diseases/d018/2010-2014.xlsx
+++ b/diseases/d018/2010-2014.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>16</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.0328075025427096</v>
       </c>
@@ -1209,9 +1206,6 @@
       <c r="O5" t="n">
         <v>11</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.02255515799811285</v>
       </c>
@@ -1505,9 +1499,6 @@
       <c r="O7" t="n">
         <v>10</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.0205046890891935</v>
       </c>
@@ -1801,9 +1792,6 @@
       <c r="O9" t="n">
         <v>15</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.03075703363379025</v>
       </c>
@@ -2097,9 +2085,6 @@
       <c r="O11" t="n">
         <v>16</v>
       </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
       <c r="R11" t="n">
         <v>0.0328075025427096</v>
       </c>
@@ -2393,9 +2378,6 @@
       <c r="O13" t="n">
         <v>22</v>
       </c>
-      <c r="Q13" t="n">
-        <v>0</v>
-      </c>
       <c r="R13" t="n">
         <v>0.0451103159962257</v>
       </c>
@@ -2689,9 +2671,6 @@
       <c r="O15" t="n">
         <v>24</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0.0492112538140644</v>
       </c>
@@ -2985,9 +2964,6 @@
       <c r="O17" t="n">
         <v>20</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.041009378178387</v>
       </c>
@@ -3281,9 +3257,6 @@
       <c r="O19" t="n">
         <v>33</v>
       </c>
-      <c r="Q19" t="n">
-        <v>0</v>
-      </c>
       <c r="R19" t="n">
         <v>0.06766547399433856</v>
       </c>
@@ -3577,9 +3550,6 @@
       <c r="O21" t="n">
         <v>81</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.1660879816224674</v>
       </c>
@@ -3873,9 +3843,6 @@
       <c r="O23" t="n">
         <v>158</v>
       </c>
-      <c r="Q23" t="n">
-        <v>0</v>
-      </c>
       <c r="R23" t="n">
         <v>0.3239740876092573</v>
       </c>
@@ -4169,9 +4136,6 @@
       <c r="O25" t="n">
         <v>67</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0.1373814168975964</v>
       </c>
@@ -4465,9 +4429,6 @@
       <c r="O27" t="n">
         <v>16</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0.03256822200315795</v>
       </c>
@@ -4761,9 +4722,6 @@
       <c r="O29" t="n">
         <v>10</v>
       </c>
-      <c r="Q29" t="n">
-        <v>0</v>
-      </c>
       <c r="R29" t="n">
         <v>0.02035513875197372</v>
       </c>
@@ -5057,9 +5015,6 @@
       <c r="O31" t="n">
         <v>13</v>
       </c>
-      <c r="Q31" t="n">
-        <v>0</v>
-      </c>
       <c r="R31" t="n">
         <v>0.02646168037756584</v>
       </c>
@@ -5353,9 +5308,6 @@
       <c r="O33" t="n">
         <v>7</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0.01424859712638161</v>
       </c>
@@ -5649,9 +5601,6 @@
       <c r="O35" t="n">
         <v>11</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.0223906526271711</v>
       </c>
@@ -5945,9 +5894,6 @@
       <c r="O37" t="n">
         <v>17</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0.03460373587835533</v>
       </c>
@@ -6241,9 +6187,6 @@
       <c r="O39" t="n">
         <v>16</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.03256822200315795</v>
       </c>
@@ -6537,9 +6480,6 @@
       <c r="O41" t="n">
         <v>13</v>
       </c>
-      <c r="Q41" t="n">
-        <v>0</v>
-      </c>
       <c r="R41" t="n">
         <v>0.02646168037756584</v>
       </c>
@@ -6833,9 +6773,6 @@
       <c r="O43" t="n">
         <v>35</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0.07124298563190803</v>
       </c>
@@ -7129,9 +7066,6 @@
       <c r="O45" t="n">
         <v>82</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.1669121377661845</v>
       </c>
@@ -7425,9 +7359,6 @@
       <c r="O47" t="n">
         <v>96</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.1954093320189478</v>
       </c>
@@ -7721,9 +7652,6 @@
       <c r="O49" t="n">
         <v>54</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.1099177492606581</v>
       </c>
@@ -8017,9 +7945,6 @@
       <c r="O51" t="n">
         <v>28</v>
       </c>
-      <c r="Q51" t="n">
-        <v>0</v>
-      </c>
       <c r="R51" t="n">
         <v>0.0564520914940418</v>
       </c>
@@ -8313,9 +8238,6 @@
       <c r="O53" t="n">
         <v>14</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.0282260457470209</v>
       </c>
@@ -8609,9 +8531,6 @@
       <c r="O55" t="n">
         <v>8</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.01612916899829766</v>
       </c>
@@ -8905,9 +8824,6 @@
       <c r="O57" t="n">
         <v>6</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.01209687674872324</v>
       </c>
@@ -9201,9 +9117,6 @@
       <c r="O59" t="n">
         <v>15</v>
       </c>
-      <c r="Q59" t="n">
-        <v>0</v>
-      </c>
       <c r="R59" t="n">
         <v>0.03024219187180811</v>
       </c>
@@ -9497,9 +9410,6 @@
       <c r="O61" t="n">
         <v>18</v>
       </c>
-      <c r="Q61" t="n">
-        <v>0</v>
-      </c>
       <c r="R61" t="n">
         <v>0.03629063024616973</v>
       </c>
@@ -9793,9 +9703,6 @@
       <c r="O63" t="n">
         <v>16</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.03225833799659531</v>
       </c>
@@ -10089,9 +9996,6 @@
       <c r="O65" t="n">
         <v>16</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0.03225833799659531</v>
       </c>
@@ -10385,9 +10289,6 @@
       <c r="O67" t="n">
         <v>17</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0.03427448412138252</v>
       </c>
@@ -11125,9 +11026,6 @@
       <c r="O72" t="n">
         <v>101</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.2036307586035079</v>
       </c>
@@ -12013,9 +11911,6 @@
       <c r="O78" t="n">
         <v>94</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.1895177357299975</v>
       </c>
@@ -13049,9 +12944,6 @@
       <c r="O85" t="n">
         <v>31</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.06250052986840342</v>
       </c>
@@ -13937,9 +13829,6 @@
       <c r="O91" t="n">
         <v>20</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.03994314931501144</v>
       </c>
@@ -14973,9 +14862,6 @@
       <c r="O98" t="n">
         <v>11</v>
       </c>
-      <c r="Q98" t="n">
-        <v>0</v>
-      </c>
       <c r="R98" t="n">
         <v>0.02196873212325629</v>
       </c>
@@ -15861,9 +15747,6 @@
       <c r="O104" t="n">
         <v>15</v>
       </c>
-      <c r="Q104" t="n">
-        <v>0</v>
-      </c>
       <c r="R104" t="n">
         <v>0.02995736198625858</v>
       </c>
@@ -16749,9 +16632,6 @@
       <c r="O110" t="n">
         <v>5</v>
       </c>
-      <c r="Q110" t="n">
-        <v>0</v>
-      </c>
       <c r="R110" t="n">
         <v>0.009985787328752859</v>
       </c>
@@ -17637,9 +17517,6 @@
       <c r="O116" t="n">
         <v>17</v>
       </c>
-      <c r="Q116" t="n">
-        <v>0</v>
-      </c>
       <c r="R116" t="n">
         <v>0.03395167691775972</v>
       </c>
@@ -18673,9 +18550,6 @@
       <c r="O123" t="n">
         <v>22</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0.04393746424651258</v>
       </c>
@@ -19561,9 +19435,6 @@
       <c r="O129" t="n">
         <v>23</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0.04593462171226315</v>
       </c>
@@ -20449,9 +20320,6 @@
       <c r="O135" t="n">
         <v>29</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0.05791756650676659</v>
       </c>
@@ -21485,9 +21353,6 @@
       <c r="O142" t="n">
         <v>29</v>
       </c>
-      <c r="Q142" t="n">
-        <v>0</v>
-      </c>
       <c r="R142" t="n">
         <v>0.05791756650676659</v>
       </c>
@@ -22373,9 +22238,6 @@
       <c r="O148" t="n">
         <v>150</v>
       </c>
-      <c r="Q148" t="n">
-        <v>0</v>
-      </c>
       <c r="R148" t="n">
         <v>0.2995736198625857</v>
       </c>
@@ -23409,9 +23271,6 @@
       <c r="O155" t="n">
         <v>154</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0.307562249725588</v>
       </c>
@@ -24297,9 +24156,6 @@
       <c r="O161" t="n">
         <v>52</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0.1038521882190298</v>
       </c>
@@ -25185,9 +25041,6 @@
       <c r="O167" t="n">
         <v>27</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0.05342402965959663</v>
       </c>
@@ -26221,9 +26074,6 @@
       <c r="O174" t="n">
         <v>8</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0.01582934212136197</v>
       </c>
@@ -27109,9 +26959,6 @@
       <c r="O180" t="n">
         <v>9</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.01780800988653221</v>
       </c>
@@ -27997,9 +27844,6 @@
       <c r="O186" t="n">
         <v>3</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0.005936003295510736</v>
       </c>
@@ -28885,9 +28729,6 @@
       <c r="O192" t="n">
         <v>8</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.01582934212136197</v>
       </c>
@@ -29921,9 +29762,6 @@
       <c r="O199" t="n">
         <v>15</v>
       </c>
-      <c r="Q199" t="n">
-        <v>0</v>
-      </c>
       <c r="R199" t="n">
         <v>0.02968001647755368</v>
       </c>
@@ -30809,9 +30647,6 @@
       <c r="O205" t="n">
         <v>9</v>
       </c>
-      <c r="Q205" t="n">
-        <v>0</v>
-      </c>
       <c r="R205" t="n">
         <v>0.01780800988653221</v>
       </c>
@@ -31845,9 +31680,6 @@
       <c r="O212" t="n">
         <v>13</v>
       </c>
-      <c r="Q212" t="n">
-        <v>0</v>
-      </c>
       <c r="R212" t="n">
         <v>0.02572268094721319</v>
       </c>
@@ -32733,9 +32565,6 @@
       <c r="O218" t="n">
         <v>32</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.06331736848544786</v>
       </c>
@@ -33621,9 +33450,6 @@
       <c r="O224" t="n">
         <v>60</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.1187200659102147</v>
       </c>
@@ -34657,9 +34483,6 @@
       <c r="O231" t="n">
         <v>82</v>
       </c>
-      <c r="Q231" t="n">
-        <v>0</v>
-      </c>
       <c r="R231" t="n">
         <v>0.1622507567439601</v>
       </c>
@@ -35544,9 +35367,6 @@
       </c>
       <c r="O237" t="n">
         <v>78</v>
-      </c>
-      <c r="Q237" t="n">
-        <v>0</v>
       </c>
       <c r="R237" t="n">
         <v>0.1543360856832791</v>
